--- a/Euro_Countries_GDP_Growth_Log.xlsx
+++ b/Euro_Countries_GDP_Growth_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unil\Master\Automne 2\Forecasting\projet_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEBC651E-5204-4CA0-A379-9D66A81AA9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5715D42-08A4-4833-8C32-ED6D6AB37CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3468" yWindow="1392" windowWidth="17232" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
